--- a/data/excel/live-entertainment-report-2026.xlsx
+++ b/data/excel/live-entertainment-report-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatthiasLavenant\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA1835C1-348B-4C75-A2FA-CCE8D9E961E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB9B2FD2-7F33-457A-99EB-5D16563D123C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4 - Casa Neos" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="10 - Mila II MM Club" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'10 - Mila II MM Club'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'11 - CN Lounge Rooftop'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'4 - Casa Neos'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'10 - Mila II MM Club'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'11 - CN Lounge Rooftop'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'4 - Casa Neos'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="20">
+  <si>
+    <t>P&amp;L - Custom by Week</t>
+  </si>
+  <si>
+    <t>07/01/2026 - 08/30/2026</t>
+  </si>
+  <si>
+    <t>4 - Casa Neos</t>
+  </si>
   <si>
     <t/>
   </si>
@@ -69,6 +78,9 @@
     <t>Week 34</t>
   </si>
   <si>
+    <t>Week 35</t>
+  </si>
+  <si>
     <t>Total Sales</t>
   </si>
   <si>
@@ -81,7 +93,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>08/24/2026 06:50 AM PDT</t>
+    <t>08/31/2026 09:20 AM PDT</t>
+  </si>
+  <si>
+    <t>11 - CN Lounge Rooftop</t>
+  </si>
+  <si>
+    <t>10 - Mila II MM Club</t>
   </si>
 </sst>
 </file>
@@ -92,12 +110,31 @@
     <numFmt numFmtId="164" formatCode="#,##0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -144,31 +181,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,7 +503,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -481,211 +530,497 @@
     <col min="22" max="22" width="1.42578125" customWidth="1"/>
     <col min="23" max="23" width="17.140625" customWidth="1"/>
     <col min="24" max="24" width="9.42578125" customWidth="1"/>
+    <col min="25" max="25" width="1.42578125" customWidth="1"/>
+    <col min="26" max="26" width="17.140625" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="9" t="s">
+    <row r="1" spans="1:27" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="9" t="s">
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="9" t="s">
+      <c r="F5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="I5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" s="9" t="s">
+      <c r="L5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="O5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="U5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
         <v>28332.26</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C6" s="3">
         <v>5.5620152630490846E-2</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3">
+      <c r="D6" s="4"/>
+      <c r="E6" s="2">
         <v>26548.799999999999</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F6" s="3">
         <v>3.6436333159464929E-2</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="2">
         <v>38131.35</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I6" s="3">
         <v>7.2556132254585709E-2</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3">
+      <c r="J6" s="4"/>
+      <c r="K6" s="2">
         <v>12676.95</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L6" s="3">
         <v>2.6158963553715716E-2</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3">
+      <c r="M6" s="4"/>
+      <c r="N6" s="2">
         <v>28158.97</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O6" s="3">
         <v>6.1815725543066954E-2</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="3">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2">
         <v>28883.95</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R6" s="3">
         <v>6.5686202205467406E-2</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="3">
+      <c r="S6" s="4"/>
+      <c r="T6" s="2">
         <v>18686.55</v>
       </c>
-      <c r="U2" s="4">
-        <v>5.0103757252912703E-2</v>
-      </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="3">
-        <v>20030</v>
-      </c>
-      <c r="X2" s="4">
-        <v>5.1815232726449258E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="U6" s="3">
+        <v>5.0110424184618037E-2</v>
+      </c>
+      <c r="V6" s="4"/>
+      <c r="W6" s="2">
+        <v>27874.31</v>
+      </c>
+      <c r="X6" s="3">
+        <v>7.2989850349689606E-2</v>
+      </c>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="2">
+        <v>20185.330000000002</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>4.9258400488139474E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
         <v>509388.39</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="3">
+      <c r="C7" s="6"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2">
         <v>728635.34</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3">
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2">
         <v>525542.76</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="3">
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="2">
         <v>484612.09</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="3">
+      <c r="L7" s="6"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2">
         <v>455530.85</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="3">
+      <c r="O7" s="6"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2">
         <v>439726.29</v>
       </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="3">
-        <v>372957.06</v>
-      </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="3">
-        <v>386565.86</v>
-      </c>
-      <c r="X3" s="7"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>13</v>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="2">
+        <v>372907.44</v>
+      </c>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="2">
+        <v>381892.96</v>
+      </c>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="2">
+        <v>409784.52</v>
+      </c>
+      <c r="AA7" s="6"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:R1"/>
+  <mergeCells count="21">
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -696,7 +1031,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -723,211 +1058,497 @@
     <col min="22" max="22" width="1.42578125" customWidth="1"/>
     <col min="23" max="23" width="17.140625" customWidth="1"/>
     <col min="24" max="24" width="9.42578125" customWidth="1"/>
+    <col min="25" max="25" width="1.42578125" customWidth="1"/>
+    <col min="26" max="26" width="17.140625" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="9" t="s">
+    <row r="1" spans="1:27" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="9" t="s">
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="9" t="s">
+      <c r="F5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="I5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" s="9" t="s">
+      <c r="L5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="O5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="U5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
         <v>6869.91</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C6" s="3">
         <v>4.5725166716008785E-2</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3">
+      <c r="D6" s="4"/>
+      <c r="E6" s="2">
         <v>21245</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F6" s="3">
         <v>8.4037269906192341E-2</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="2">
         <v>53600</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I6" s="3">
         <v>0.40995539975890649</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3">
+      <c r="J6" s="4"/>
+      <c r="K6" s="2">
         <v>14650</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L6" s="3">
         <v>0.11672648268129575</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3">
+      <c r="M6" s="4"/>
+      <c r="N6" s="2">
         <v>4650</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O6" s="3">
         <v>5.8343789209535757E-2</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="3">
-        <v>9560</v>
-      </c>
-      <c r="R2" s="4">
-        <v>6.6679412221890666E-2</v>
-      </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="3">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2">
+        <v>5876.81</v>
+      </c>
+      <c r="R6" s="3">
+        <v>6.9632925340948143E-2</v>
+      </c>
+      <c r="S6" s="4"/>
+      <c r="T6" s="2">
         <v>8750</v>
       </c>
-      <c r="U2" s="4">
-        <v>5.9550372230660988E-2</v>
-      </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="3">
-        <v>11074</v>
-      </c>
-      <c r="X2" s="4">
-        <v>3.935843621486728E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="U6" s="3">
+        <v>5.9931564317938391E-2</v>
+      </c>
+      <c r="V6" s="4"/>
+      <c r="W6" s="2">
+        <v>9739.36</v>
+      </c>
+      <c r="X6" s="3">
+        <v>8.2983689736483915E-2</v>
+      </c>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="2">
+        <v>-2400</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>-2.5842060861283583E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
         <v>150243.51999999999</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="3">
+      <c r="C7" s="6"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2">
         <v>252804.5</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3">
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2">
         <v>130745.93</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="3">
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="2">
         <v>125507.08</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="3">
+      <c r="L7" s="6"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2">
         <v>79700</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="3">
-        <v>88135.3</v>
-      </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="3">
-        <v>146934.43</v>
-      </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="3">
-        <v>117509.75</v>
-      </c>
-      <c r="X3" s="7"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>13</v>
+      <c r="O7" s="6"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2">
+        <v>84397</v>
+      </c>
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="2">
+        <v>145999.85999999999</v>
+      </c>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="2">
+        <v>117364.75</v>
+      </c>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="2">
+        <v>92871.85</v>
+      </c>
+      <c r="AA7" s="6"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:R1"/>
+  <mergeCells count="21">
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -938,7 +1559,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -965,211 +1586,497 @@
     <col min="22" max="22" width="1.42578125" customWidth="1"/>
     <col min="23" max="23" width="17.140625" customWidth="1"/>
     <col min="24" max="24" width="9.42578125" customWidth="1"/>
+    <col min="25" max="25" width="1.42578125" customWidth="1"/>
+    <col min="26" max="26" width="17.140625" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="9" t="s">
+    <row r="1" spans="1:27" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="9" t="s">
+      <c r="C5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="9" t="s">
+      <c r="F5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="I5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" s="9" t="s">
+      <c r="L5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="O5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="T5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="U5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
         <v>11125.95</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C6" s="3">
         <v>5.5282850115525084E-2</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3">
+      <c r="D6" s="4"/>
+      <c r="E6" s="2">
         <v>21215.1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F6" s="3">
         <v>6.2714383371824473E-2</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3">
+      <c r="G6" s="4"/>
+      <c r="H6" s="2">
         <v>17205</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I6" s="3">
         <v>7.3823455571903077E-2</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="3">
+      <c r="J6" s="4"/>
+      <c r="K6" s="2">
         <v>21970</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L6" s="3">
         <v>5.9200342149414879E-2</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3">
-        <v>20540</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0.1179605572975891</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="3">
-        <v>24000</v>
-      </c>
-      <c r="R2" s="4">
+      <c r="M6" s="4"/>
+      <c r="N6" s="2">
+        <v>22040</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.12657500890159998</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2">
+        <v>20035</v>
+      </c>
+      <c r="R6" s="3">
         <v>0.1133089202143453</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="3">
+      <c r="S6" s="4"/>
+      <c r="T6" s="2">
         <v>19300</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U6" s="3">
         <v>0.11426068011745762</v>
       </c>
-      <c r="V2" s="5"/>
-      <c r="W2" s="3">
-        <v>36000</v>
-      </c>
-      <c r="X2" s="4">
-        <v>0.16154684726910781</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="V6" s="4"/>
+      <c r="W6" s="2">
+        <v>33957.440000000002</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.17986002699374987</v>
+      </c>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="2">
+        <v>850</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>3.6342412394797801E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
         <v>201255</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="3">
+      <c r="C7" s="6"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="2">
         <v>338281.25</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3">
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="2">
         <v>233056.01</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="3">
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="2">
         <v>371112.72</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="3">
+      <c r="L7" s="6"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2">
         <v>174126</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="3">
+      <c r="O7" s="6"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2">
         <v>176817.5</v>
       </c>
-      <c r="R3" s="7"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="3">
+      <c r="R7" s="6"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="2">
         <v>168912</v>
       </c>
-      <c r="U3" s="7"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="3">
-        <v>189883</v>
-      </c>
-      <c r="X3" s="7"/>
-    </row>
-    <row r="6" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>13</v>
+      <c r="U7" s="6"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="2">
+        <v>188799.26</v>
+      </c>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="2">
+        <v>233886.51</v>
+      </c>
+      <c r="AA7" s="6"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:R1"/>
+  <mergeCells count="21">
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="S5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
